--- a/Assets/GameSample/Forms/Excels/Story/Skill/SkillProduct_Product.xlsx
+++ b/Assets/GameSample/Forms/Excels/Story/Skill/SkillProduct_Product.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9060"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="38">
   <si>
     <t>uid</t>
   </si>
@@ -42,6 +42,9 @@
     <t>name</t>
   </si>
   <si>
+    <t>desc</t>
+  </si>
+  <si>
     <t>labId</t>
   </si>
   <si>
@@ -78,19 +81,22 @@
     <t>write;override;uniqueIndex1</t>
   </si>
   <si>
+    <t>write</t>
+  </si>
+  <si>
     <t>write;index;index2;override</t>
   </si>
   <si>
     <t>write;index;index2;uniqueIndex1;override</t>
   </si>
   <si>
-    <t>write</t>
-  </si>
-  <si>
     <t>write;enum:SkillType;custom</t>
   </si>
   <si>
     <t>名称</t>
+  </si>
+  <si>
+    <t>描述</t>
   </si>
   <si>
     <t>标签</t>
@@ -763,14 +769,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1092,22 +1095,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="38.3583333333333" customWidth="1"/>
-    <col min="3" max="3" width="31.9166666666667" customWidth="1"/>
-    <col min="4" max="4" width="39.075" customWidth="1"/>
-    <col min="6" max="6" width="34.8" customWidth="1"/>
-    <col min="7" max="8" width="31.4583333333333" customWidth="1"/>
-    <col min="9" max="10" width="21.15" customWidth="1"/>
-    <col min="11" max="11" width="41.825" customWidth="1"/>
-    <col min="12" max="12" width="21.5333333333333" customWidth="1"/>
-    <col min="13" max="13" width="14.8" customWidth="1"/>
+    <col min="2" max="3" width="38.3583333333333" customWidth="1"/>
+    <col min="4" max="4" width="31.9166666666667" customWidth="1"/>
+    <col min="5" max="5" width="39.075" customWidth="1"/>
+    <col min="7" max="7" width="34.8" customWidth="1"/>
+    <col min="8" max="9" width="31.4583333333333" customWidth="1"/>
+    <col min="10" max="11" width="21.15" customWidth="1"/>
+    <col min="12" max="12" width="41.825" customWidth="1"/>
+    <col min="13" max="13" width="21.5333333333333" customWidth="1"/>
+    <col min="14" max="14" width="14.8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1117,16 +1120,16 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H1" t="s">
@@ -1144,150 +1147,163 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" t="s">
         <v>15</v>
       </c>
+      <c r="D2" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="E2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" t="s">
         <v>17</v>
       </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L2" t="s">
-        <v>16</v>
+        <v>15</v>
+      </c>
+      <c r="M2" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:13">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
         <v>20</v>
       </c>
+      <c r="D3" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="E3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G3" t="s">
+      <c r="F3" t="s">
         <v>23</v>
       </c>
+      <c r="G3" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="H3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L3" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="M3" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" t="s">
-        <v>29</v>
+        <v>32</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="E4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G4" t="s">
-        <v>32</v>
+      <c r="F4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="H4" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L4" t="s">
-        <v>29</v>
+        <v>36</v>
+      </c>
+      <c r="M4" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:13">
       <c r="A5" s="1">
         <v>0</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
-      <c r="G5" t="s">
-        <v>35</v>
+      <c r="D5" s="1"/>
+      <c r="H5" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:13">
       <c r="A6" s="2"/>
-      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:13">
       <c r="A7" s="2"/>
-      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:13">
       <c r="A8" s="2"/>
-      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:13">
       <c r="A9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="F9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="G9" s="2"/>
     </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="3"/>
-      <c r="D10" s="2"/>
-      <c r="F10" s="2"/>
+    <row r="10" spans="1:13">
+      <c r="A10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="G10" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
